--- a/أسعار_ورشة_المدرسة_للتعبئة.xlsx
+++ b/أسعار_ورشة_المدرسة_للتعبئة.xlsx
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I127"/>
+  <dimension ref="A1:I126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -562,32 +562,32 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>900900</t>
+          <t>700203</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>فاتورة يدوية سابقة (بدون بنود)</t>
+          <t>باكيت مسمار بولاذ 6 سم</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>خردوات</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G3" s="5" t="inlineStr">
-        <is>
-          <t>63.500 / 183.850 / 184.400 / 188.400 / 202.000 / 512.750</t>
+        <v>1</v>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>1.500</t>
         </is>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="I3" s="4" t="n"/>
     </row>
@@ -597,12 +597,12 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>700203</t>
+          <t>700202</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>باكيت مسمار بولاذ 6 سم</t>
+          <t>باكيت مسمار بولاذ 8 سم</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -618,11 +618,11 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1.500</t>
+          <t>1.750</t>
         </is>
       </c>
       <c r="H4" s="2" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="I4" s="4" t="n"/>
     </row>
@@ -632,12 +632,12 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>700202</t>
+          <t>200345</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>باكيت مسمار بولاذ 8 سم</t>
+          <t>باكيت ورق حف كابتن نعومة 40 تايلندي</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -646,18 +646,18 @@
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1.750</t>
+          <t>20.000</t>
         </is>
       </c>
       <c r="H5" s="2" t="n">
-        <v>1.75</v>
+        <v>20</v>
       </c>
       <c r="I5" s="4" t="n"/>
     </row>
@@ -667,12 +667,12 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>200345</t>
+          <t>701765</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>باكيت ورق حف كابتن نعومة 40 تايلندي</t>
+          <t>بربيش ماء 3/4 انش 25 متر اتقان</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -688,11 +688,11 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>20.000</t>
+          <t>23.000</t>
         </is>
       </c>
       <c r="H6" s="2" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I6" s="4" t="n"/>
     </row>
@@ -702,12 +702,12 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>701765</t>
+          <t>100310</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>بربيش ماء 3/4 انش 25 متر اتقان</t>
+          <t>تفلون مواسير 10م</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -716,18 +716,18 @@
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1</v>
+        <v>105</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>23.000</t>
+          <t>0.250</t>
         </is>
       </c>
       <c r="H7" s="2" t="n">
-        <v>23</v>
+        <v>0.25</v>
       </c>
       <c r="I7" s="4" t="n"/>
     </row>
@@ -737,12 +737,12 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>100310</t>
+          <t>100129</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>تفلون مواسير 10م</t>
+          <t>خيط بناء مصيص سماكة 0.85 ملي</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -751,18 +751,18 @@
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>105</v>
+        <v>3</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>0.250</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="I8" s="4" t="n"/>
     </row>
@@ -772,12 +772,12 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>100129</t>
+          <t>100434</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>خيط بناء مصيص سماكة 0.85 ملي</t>
+          <t>زاوية قصارة 2.85م</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -786,18 +786,18 @@
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>3</v>
+        <v>100</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.700</t>
         </is>
       </c>
       <c r="H9" s="2" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="I9" s="4" t="n"/>
     </row>
@@ -807,12 +807,12 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>100434</t>
+          <t>700478</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>زاوية قصارة 2.85م</t>
+          <t>سلك بناء اسود مجدول</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -821,18 +821,18 @@
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0.700</t>
+          <t>2.250</t>
         </is>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0.7</v>
+        <v>2.25</v>
       </c>
       <c r="I10" s="4" t="n"/>
     </row>
@@ -842,12 +842,12 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>700478</t>
+          <t>900037</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>سلك بناء اسود مجدول</t>
+          <t>سلك ناعم ابيض</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -856,18 +856,18 @@
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>5</v>
+        <v>110</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>2.250</t>
+        <v>7</v>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>1.250 / 1.500</t>
         </is>
       </c>
       <c r="H11" s="2" t="n">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
       <c r="I11" s="4" t="n"/>
     </row>
@@ -877,12 +877,12 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>900037</t>
+          <t>700391</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>سلك ناعم ابيض</t>
+          <t>سلم خليلي 6 درجات</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -891,18 +891,18 @@
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>110</v>
+        <v>1</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="G12" s="5" t="inlineStr">
-        <is>
-          <t>1.250 / 1.500</t>
+        <v>1</v>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>24.000</t>
         </is>
       </c>
       <c r="H12" s="2" t="n">
-        <v>1.5</v>
+        <v>24</v>
       </c>
       <c r="I12" s="4" t="n"/>
     </row>
@@ -912,12 +912,12 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>700391</t>
+          <t>100435</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>سلم خليلي 6 درجات</t>
+          <t>شبك قصارة 15 سم - 17 م اماراتي</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -926,18 +926,18 @@
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>24.000</t>
+          <t>3.500</t>
         </is>
       </c>
       <c r="H13" s="2" t="n">
-        <v>24</v>
+        <v>3.5</v>
       </c>
       <c r="I13" s="4" t="n"/>
     </row>
@@ -947,12 +947,12 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>100435</t>
+          <t>900089</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>شبك قصارة 15 سم - 17 م اماراتي</t>
+          <t>طورية مع عصا</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -961,18 +961,18 @@
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="F14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>5.000</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="n">
         <v>5</v>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>3.500</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="n">
-        <v>3.5</v>
       </c>
       <c r="I14" s="4" t="n"/>
     </row>
@@ -982,12 +982,12 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>900089</t>
+          <t>702555</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>طورية مع عصا</t>
+          <t>فرشاة سلك نحاس</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -996,18 +996,18 @@
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F15" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5.000</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="H15" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I15" s="4" t="n"/>
     </row>
@@ -1017,12 +1017,12 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>702555</t>
+          <t>701704</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>فرشاة سلك نحاس</t>
+          <t>كريك 27 سم مع عصا</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -1038,11 +1038,11 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>5.000</t>
         </is>
       </c>
       <c r="H16" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I16" s="4" t="n"/>
     </row>
@@ -1052,12 +1052,12 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>701704</t>
+          <t>100325</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>كريك 27 سم مع عصا</t>
+          <t>مربط بربيش غاز 3/4 انش</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1066,18 +1066,18 @@
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F17" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5.000</t>
+          <t>0.250</t>
         </is>
       </c>
       <c r="H17" s="2" t="n">
-        <v>5</v>
+        <v>0.25</v>
       </c>
       <c r="I17" s="4" t="n"/>
     </row>
@@ -1087,12 +1087,12 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>100325</t>
+          <t>900069</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>مربط بربيش غاز 3/4 انش</t>
+          <t>مسمار بناء 10 سم</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1101,18 +1101,18 @@
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F18" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0.250</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="H18" s="2" t="n">
-        <v>0.25</v>
+        <v>1.9</v>
       </c>
       <c r="I18" s="4" t="n"/>
     </row>
@@ -1122,12 +1122,12 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>900069</t>
+          <t>900070</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>مسمار بناء 10 سم</t>
+          <t>مسمار بناء 6 سم</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1136,10 +1136,10 @@
         </is>
       </c>
       <c r="E19" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="F19" s="2" t="n">
         <v>3</v>
-      </c>
-      <c r="F19" s="2" t="n">
-        <v>1</v>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>900070</t>
+          <t>700012</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>مسمار بناء 6 سم</t>
+          <t>مصلب بلاط هندسي 2 ملي (تعبئة 100)</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1171,18 +1171,18 @@
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.500</t>
         </is>
       </c>
       <c r="H20" s="2" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="I20" s="4" t="n"/>
     </row>
@@ -1192,12 +1192,12 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>700012</t>
+          <t>900061</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>مصلب بلاط هندسي 2 ملي (تعبئة 100)</t>
+          <t>مصلب بلاط هندسي 2 ملي (تعبئة 200)</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1206,18 +1206,18 @@
         </is>
       </c>
       <c r="E21" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>2.000</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="n">
         <v>2</v>
-      </c>
-      <c r="F21" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>1.500</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="n">
-        <v>1.5</v>
       </c>
       <c r="I21" s="4" t="n"/>
     </row>
@@ -1227,12 +1227,12 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>900061</t>
+          <t>076174145632</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>مصلب بلاط هندسي 2 ملي (تعبئة 200)</t>
+          <t>مقص صاج FATMAX</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -1241,18 +1241,18 @@
         </is>
       </c>
       <c r="E22" s="2" t="n">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>5.000</t>
         </is>
       </c>
       <c r="H22" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I22" s="4" t="n"/>
     </row>
@@ -1262,32 +1262,32 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>076174145632</t>
+          <t>200001</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>مقص صاج FATMAX</t>
+          <t>درم املشن ديلوكس ابيض</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>خردوات</t>
+          <t>دهانات</t>
         </is>
       </c>
       <c r="E23" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F23" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>5.000</t>
+          <t>21.000</t>
         </is>
       </c>
       <c r="H23" s="2" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="I23" s="4" t="n"/>
     </row>
@@ -1297,12 +1297,12 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>200001</t>
+          <t>200004</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>درم املشن ديلوكس ابيض</t>
+          <t>درم املشن ناشونال توب 800</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1311,10 +1311,10 @@
         </is>
       </c>
       <c r="E24" s="2" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
@@ -1332,12 +1332,12 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>200004</t>
+          <t>200346</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>درم املشن ناشونال توب 800</t>
+          <t>درم املشن ناشونال توب 802</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1346,10 +1346,10 @@
         </is>
       </c>
       <c r="E25" s="2" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
@@ -1367,12 +1367,12 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>200346</t>
+          <t>200343</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>درم املشن ناشونال توب 802</t>
+          <t>شوال معجونة تيراكو 25 كغم</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -1381,18 +1381,18 @@
         </is>
       </c>
       <c r="E26" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F26" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>21.000</t>
+          <t>5.000</t>
         </is>
       </c>
       <c r="H26" s="2" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="I26" s="4" t="n"/>
     </row>
@@ -1402,12 +1402,12 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>200343</t>
+          <t>200260</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>شوال معجونة تيراكو 25 كغم</t>
+          <t>شوال معجونة جدران 25 كغم القدس</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1423,11 +1423,11 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>5.000</t>
+          <t>6.000</t>
         </is>
       </c>
       <c r="H27" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I27" s="4" t="n"/>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>200260</t>
+          <t>200297</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>شوال معجونة جدران 25 كغم القدس</t>
+          <t>شوال معجونة ديلوكس جدران 25 كغم</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -1451,18 +1451,18 @@
         </is>
       </c>
       <c r="E28" s="2" t="n">
-        <v>5</v>
+        <v>43</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>6.000</t>
+          <t>5.500</t>
         </is>
       </c>
       <c r="H28" s="2" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="I28" s="4" t="n"/>
     </row>
@@ -1472,12 +1472,12 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>200297</t>
+          <t>200210</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>شوال معجونة ديلوكس جدران 25 كغم</t>
+          <t>صبغة هندي صحراوي</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -1486,18 +1486,18 @@
         </is>
       </c>
       <c r="E29" s="2" t="n">
-        <v>43</v>
+        <v>4</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>5.500</t>
+          <t>1.500</t>
         </is>
       </c>
       <c r="H29" s="2" t="n">
-        <v>5.5</v>
+        <v>1.5</v>
       </c>
       <c r="I29" s="4" t="n"/>
     </row>
@@ -1507,12 +1507,12 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>200210</t>
+          <t>200299</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>صبغة هندي صحراوي</t>
+          <t>لاصق بلاط اراسيا</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -1521,18 +1521,18 @@
         </is>
       </c>
       <c r="E30" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F30" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>1.500</t>
+          <t>5.000</t>
         </is>
       </c>
       <c r="H30" s="2" t="n">
-        <v>1.5</v>
+        <v>5</v>
       </c>
       <c r="I30" s="4" t="n"/>
     </row>
@@ -1542,12 +1542,12 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>200299</t>
+          <t>200342</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>لاصق بلاط اراسيا</t>
+          <t>لاصق بلاط سافيتو</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -1556,10 +1556,10 @@
         </is>
       </c>
       <c r="E31" s="2" t="n">
-        <v>6</v>
+        <v>60</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
@@ -1577,32 +1577,32 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>200342</t>
+          <t>500082</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>لاصق بلاط سافيتو</t>
+          <t>11/4" ماسورة (شانيل) سعودي</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>دهانات</t>
+          <t>صحي</t>
         </is>
       </c>
       <c r="E32" s="2" t="n">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>5.000</t>
+          <t>29.000</t>
         </is>
       </c>
       <c r="H32" s="2" t="n">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="I32" s="4" t="n"/>
     </row>
@@ -1612,12 +1612,12 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>500082</t>
+          <t>500086</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>11/4" ماسورة (شانيل) سعودي</t>
+          <t>3/4" ماسورة (خارجي) سعودي</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -1626,18 +1626,18 @@
         </is>
       </c>
       <c r="E33" s="2" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F33" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>29.000</t>
+          <t>6.500</t>
         </is>
       </c>
       <c r="H33" s="2" t="n">
-        <v>29</v>
+        <v>6.5</v>
       </c>
       <c r="I33" s="4" t="n"/>
     </row>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>500086</t>
+          <t>500381</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>3/4" ماسورة (خارجي) سعودي</t>
+          <t>اجو (احمر) 1/4 ك شنل امريكي</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -1661,18 +1661,18 @@
         </is>
       </c>
       <c r="E34" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F34" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>6.500</t>
+          <t>2.500</t>
         </is>
       </c>
       <c r="H34" s="2" t="n">
-        <v>6.5</v>
+        <v>3.5</v>
       </c>
       <c r="I34" s="4" t="n"/>
     </row>
@@ -1682,12 +1682,12 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>500381</t>
+          <t>500377</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>اجو (احمر) 1/4 ك شنل امريكي</t>
+          <t>اجو (اسود) 1 ك شنل امريكي</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -1696,18 +1696,18 @@
         </is>
       </c>
       <c r="E35" s="2" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>2.500</t>
+        <v>4</v>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>5.750 / 6.000</t>
         </is>
       </c>
       <c r="H35" s="2" t="n">
-        <v>3.5</v>
+        <v>6</v>
       </c>
       <c r="I35" s="4" t="n"/>
     </row>
@@ -1717,12 +1717,12 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>500377</t>
+          <t>500378</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>اجو (اسود) 1 ك شنل امريكي</t>
+          <t>اجو (اسود) 1/2 ك شنل امريكي</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -1731,18 +1731,18 @@
         </is>
       </c>
       <c r="E36" s="2" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="G36" s="5" t="inlineStr">
-        <is>
-          <t>5.750 / 6.000</t>
+        <v>1</v>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>4.500</t>
         </is>
       </c>
       <c r="H36" s="2" t="n">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="I36" s="4" t="n"/>
     </row>
@@ -1752,12 +1752,12 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>500378</t>
+          <t>500529</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>اجو (اسود) 1/2 ك شنل امريكي</t>
+          <t>ادبتر انثى سعودي 11/4" * 11/4"</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -1766,18 +1766,18 @@
         </is>
       </c>
       <c r="E37" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F37" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>4.500</t>
+          <t>3.500</t>
         </is>
       </c>
       <c r="H37" s="2" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="I37" s="4" t="n"/>
     </row>
@@ -1787,12 +1787,12 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>500529</t>
+          <t>500527</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>ادبتر انثى سعودي 11/4" * 11/4"</t>
+          <t>ادبتر انثى سعودي 3/4 * 3/4</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -1801,18 +1801,18 @@
         </is>
       </c>
       <c r="E38" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F38" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>3.500</t>
+          <t>1.500</t>
         </is>
       </c>
       <c r="H38" s="2" t="n">
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
       <c r="I38" s="4" t="n"/>
     </row>
@@ -1822,12 +1822,12 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>500527</t>
+          <t>500523</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>ادبتر انثى سعودي 3/4 * 3/4</t>
+          <t>ادبتر ذكر سعودي 11/4" * 11/4"</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -1836,18 +1836,18 @@
         </is>
       </c>
       <c r="E39" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>1.500</t>
+          <t>2.500</t>
         </is>
       </c>
       <c r="H39" s="2" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="I39" s="4" t="n"/>
     </row>
@@ -1857,12 +1857,12 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>500523</t>
+          <t>500521</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>ادبتر ذكر سعودي 11/4" * 11/4"</t>
+          <t>ادبتر ذكر سعودي 3/4 * 3/4</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -1878,11 +1878,11 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>2.500</t>
+          <t>1.250</t>
         </is>
       </c>
       <c r="H40" s="2" t="n">
-        <v>2.5</v>
+        <v>1.25</v>
       </c>
       <c r="I40" s="4" t="n"/>
     </row>
@@ -1892,12 +1892,12 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>500521</t>
+          <t>500600</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>ادبتر ذكر سعودي 3/4 * 3/4</t>
+          <t>باكيت براغي 3.5 سم</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -1906,18 +1906,18 @@
         </is>
       </c>
       <c r="E41" s="2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>1.250</t>
+          <t>3.500</t>
         </is>
       </c>
       <c r="H41" s="2" t="n">
-        <v>1.25</v>
+        <v>3.5</v>
       </c>
       <c r="I41" s="4" t="n"/>
     </row>
@@ -1927,12 +1927,12 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>500600</t>
+          <t>500786</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>باكيت براغي 3.5 سم</t>
+          <t>بربيش كيزر (اسباني/ايطالي) 40 سم</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -1941,18 +1941,18 @@
         </is>
       </c>
       <c r="E42" s="2" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="F42" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>3.500</t>
+          <t>1.500</t>
         </is>
       </c>
       <c r="H42" s="2" t="n">
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
       <c r="I42" s="4" t="n"/>
     </row>
@@ -1962,12 +1962,12 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>500786</t>
+          <t>500833</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>بربيش كيزر (اسباني/ايطالي) 40 سم</t>
+          <t>بكس بلاستيك اردني 16ملم - لفة 100 متر</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -1976,18 +1976,18 @@
         </is>
       </c>
       <c r="E43" s="2" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="F43" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>1.500</t>
+          <t>30.000</t>
         </is>
       </c>
       <c r="H43" s="2" t="n">
-        <v>1.5</v>
+        <v>30</v>
       </c>
       <c r="I43" s="4" t="n"/>
     </row>
@@ -1997,12 +1997,12 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>500833</t>
+          <t>500596</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>بكس بلاستيك اردني 16ملم - لفة 100 متر</t>
+          <t>بكس بلاستيك ايطالي 16ملم - لفة 100 متر</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -2011,18 +2011,18 @@
         </is>
       </c>
       <c r="E44" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>30.000</t>
+        <v>2</v>
+      </c>
+      <c r="G44" s="5" t="inlineStr">
+        <is>
+          <t>0.000 / 35.000</t>
         </is>
       </c>
       <c r="H44" s="2" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I44" s="4" t="n"/>
     </row>
@@ -2032,12 +2032,12 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>500596</t>
+          <t>500598</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>بكس بلاستيك ايطالي 16ملم - لفة 100 متر</t>
+          <t>بكس بلاستيك ايطالي 20ملم - لفة 100 متر</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -2046,18 +2046,18 @@
         </is>
       </c>
       <c r="E45" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>0.000 / 35.000</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="H45" s="2" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="I45" s="4" t="n"/>
     </row>
@@ -2067,12 +2067,12 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>500598</t>
+          <t>500653</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>بكس بلاستيك ايطالي 20ملم - لفة 100 متر</t>
+          <t>بكس بلاستيك ايطالي SESTA ازرق 16ملم - لفة 100 متر</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -2081,18 +2081,18 @@
         </is>
       </c>
       <c r="E46" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F46" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="G46" s="5" t="inlineStr">
-        <is>
-          <t>0.000</t>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>38.000</t>
         </is>
       </c>
       <c r="H46" s="2" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="I46" s="4" t="n"/>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>500653</t>
+          <t>500487</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>بكس بلاستيك ايطالي SESTA ازرق 16ملم - لفة 100 متر</t>
+          <t>تي T سعودي 11/4"</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -2116,18 +2116,18 @@
         </is>
       </c>
       <c r="E47" s="2" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="F47" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>38.000</t>
+          <t>1.250</t>
         </is>
       </c>
       <c r="H47" s="2" t="n">
-        <v>38</v>
+        <v>1.25</v>
       </c>
       <c r="I47" s="4" t="n"/>
     </row>
@@ -2137,12 +2137,12 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>500487</t>
+          <t>500485</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>تي T سعودي 11/4"</t>
+          <t>تي T سعودي 3/4"</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -2151,18 +2151,18 @@
         </is>
       </c>
       <c r="E48" s="2" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>1.250</t>
+          <t>0.800</t>
         </is>
       </c>
       <c r="H48" s="2" t="n">
-        <v>1.25</v>
+        <v>0.8</v>
       </c>
       <c r="I48" s="4" t="n"/>
     </row>
@@ -2172,12 +2172,12 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>500485</t>
+          <t>500426</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>تي T سعودي 3/4"</t>
+          <t>تي بلاستيك 6" ضغط صغير ومرار</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -2186,18 +2186,18 @@
         </is>
       </c>
       <c r="E49" s="2" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>0.800</t>
+          <t>6.500</t>
         </is>
       </c>
       <c r="H49" s="2" t="n">
-        <v>0.8</v>
+        <v>6.5</v>
       </c>
       <c r="I49" s="4" t="n"/>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>500426</t>
+          <t>500435</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>تي بلاستيك 6" ضغط صغير ومرار</t>
+          <t>تي مع باب بلاستيك 4" ضغط صغير ومرار</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -2221,18 +2221,18 @@
         </is>
       </c>
       <c r="E50" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F50" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>6.500</t>
+          <t>3.900</t>
         </is>
       </c>
       <c r="H50" s="2" t="n">
-        <v>6.5</v>
+        <v>3.9</v>
       </c>
       <c r="I50" s="4" t="n"/>
     </row>
@@ -2242,12 +2242,12 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>500435</t>
+          <t>500269</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>تي مع باب بلاستيك 4" ضغط صغير ومرار</t>
+          <t>جلدة تدكيك كاب 32 احمروازرق</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -2256,18 +2256,18 @@
         </is>
       </c>
       <c r="E51" s="2" t="n">
-        <v>4</v>
+        <v>125</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>3.900</t>
+          <t>0.050</t>
         </is>
       </c>
       <c r="H51" s="2" t="n">
-        <v>3.9</v>
+        <v>0.05</v>
       </c>
       <c r="I51" s="4" t="n"/>
     </row>
@@ -2277,12 +2277,12 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>500269</t>
+          <t>500590</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>جلدة تدكيك كاب 32 احمروازرق</t>
+          <t>جلدة تدكيك كاب 40 احمروازرق</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -2291,18 +2291,18 @@
         </is>
       </c>
       <c r="E52" s="2" t="n">
-        <v>125</v>
+        <v>8</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>0.050</t>
+          <t>0.100</t>
         </is>
       </c>
       <c r="H52" s="2" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="I52" s="4" t="n"/>
     </row>
@@ -2312,12 +2312,12 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>500590</t>
+          <t>500264</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>جلدة تدكيك كاب 40 احمروازرق</t>
+          <t>جلدة مانجيت 11/4"</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -2326,18 +2326,18 @@
         </is>
       </c>
       <c r="E53" s="2" t="n">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>0.100</t>
+          <t>0.250</t>
         </is>
       </c>
       <c r="H53" s="2" t="n">
-        <v>0.1</v>
+        <v>0.25</v>
       </c>
       <c r="I53" s="4" t="n"/>
     </row>
@@ -2347,12 +2347,12 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>500264</t>
+          <t>500197</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>جلدة مانجيت 11/4"</t>
+          <t>حنفية ستيم (ايطالي) 3/4"</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -2361,18 +2361,18 @@
         </is>
       </c>
       <c r="E54" s="2" t="n">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G54" s="2" t="inlineStr">
-        <is>
-          <t>0.250</t>
+        <v>3</v>
+      </c>
+      <c r="G54" s="5" t="inlineStr">
+        <is>
+          <t>4.000 / 5.000</t>
         </is>
       </c>
       <c r="H54" s="2" t="n">
-        <v>0.25</v>
+        <v>4</v>
       </c>
       <c r="I54" s="4" t="n"/>
     </row>
@@ -2382,12 +2382,12 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>500197</t>
+          <t>500202</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>حنفية ستيم (ايطالي) 3/4"</t>
+          <t>خزانة بكس 1 متر</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -2396,18 +2396,18 @@
         </is>
       </c>
       <c r="E55" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="G55" s="5" t="inlineStr">
-        <is>
-          <t>4.000 / 5.000</t>
+        <v>1</v>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>18.000</t>
         </is>
       </c>
       <c r="H55" s="2" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="I55" s="4" t="n"/>
     </row>
@@ -2417,12 +2417,12 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>500202</t>
+          <t>500203</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>خزانة بكس 1 متر</t>
+          <t>خزانة بكس 1.2 متر</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -2438,11 +2438,11 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>18.000</t>
+          <t>23.000</t>
         </is>
       </c>
       <c r="H56" s="2" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I56" s="4" t="n"/>
     </row>
@@ -2452,12 +2452,12 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>500203</t>
+          <t>500832</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>خزانة بكس 1.2 متر</t>
+          <t>دعسة حمام عربي شرعي</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -2466,18 +2466,18 @@
         </is>
       </c>
       <c r="E57" s="2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F57" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>23.000</t>
+          <t>11.000</t>
         </is>
       </c>
       <c r="H57" s="2" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="I57" s="4" t="n"/>
     </row>
@@ -2487,12 +2487,12 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>500832</t>
+          <t>500695</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>دعسة حمام عربي شرعي</t>
+          <t>سدة بلاستيك طويلة فحص 1/2"</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -2501,18 +2501,18 @@
         </is>
       </c>
       <c r="E58" s="2" t="n">
-        <v>8</v>
+        <v>50</v>
       </c>
       <c r="F58" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>11.000</t>
+          <t>0.100</t>
         </is>
       </c>
       <c r="H58" s="2" t="n">
-        <v>11</v>
+        <v>0.1</v>
       </c>
       <c r="I58" s="4" t="n"/>
     </row>
@@ -2522,12 +2522,12 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>500695</t>
+          <t>500504</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>سدة بلاستيك طويلة فحص 1/2"</t>
+          <t>سدة سعودي 11/4"</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -2536,18 +2536,18 @@
         </is>
       </c>
       <c r="E59" s="2" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="F59" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>0.100</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="H59" s="2" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="I59" s="4" t="n"/>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>500504</t>
+          <t>500456</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>سدة سعودي 11/4"</t>
+          <t>سدة كبس بلاستيك 2" ضغط صغير ومرار</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -2571,18 +2571,18 @@
         </is>
       </c>
       <c r="E60" s="2" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.700</t>
         </is>
       </c>
       <c r="H60" s="2" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="I60" s="4" t="n"/>
     </row>
@@ -2592,12 +2592,12 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>500456</t>
+          <t>500454</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>سدة كبس بلاستيك 2" ضغط صغير ومرار</t>
+          <t>سدة كبس بلاستيك 4" ضغط صغير ومرار</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -2606,18 +2606,18 @@
         </is>
       </c>
       <c r="E61" s="2" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>0.700</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="H61" s="2" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="I61" s="4" t="n"/>
     </row>
@@ -2627,12 +2627,12 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>500454</t>
+          <t>500457</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>سدة كبس بلاستيك 4" ضغط صغير ومرار</t>
+          <t>سدة مع باب بلاستيك 6" ضغط صغير ومرار</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -2641,18 +2641,18 @@
         </is>
       </c>
       <c r="E62" s="2" t="n">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>3.600</t>
         </is>
       </c>
       <c r="H62" s="2" t="n">
-        <v>1</v>
+        <v>3.6</v>
       </c>
       <c r="I62" s="4" t="n"/>
     </row>
@@ -2662,12 +2662,12 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>500457</t>
+          <t>500146</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>سدة مع باب بلاستيك 6" ضغط صغير ومرار</t>
+          <t>سدة نحاس ايطالي 1/2"</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -2683,11 +2683,11 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>3.600</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="H63" s="2" t="n">
-        <v>3.6</v>
+        <v>1</v>
       </c>
       <c r="I63" s="4" t="n"/>
     </row>
@@ -2697,12 +2697,12 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>500146</t>
+          <t>500397</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>سدة نحاس ايطالي 1/2"</t>
+          <t>سليف حلزوني احمر وازرق 32ملم - لفة 50 متر</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -2711,18 +2711,18 @@
         </is>
       </c>
       <c r="E64" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="F64" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F64" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>10.000</t>
         </is>
       </c>
       <c r="H64" s="2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I64" s="4" t="n"/>
     </row>
@@ -2732,12 +2732,12 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>500397</t>
+          <t>900090</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>سليف حلزوني احمر وازرق 32ملم - لفة 50 متر</t>
+          <t>سيفون قطعة واحدة 4" صغير ومرار</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -2746,18 +2746,18 @@
         </is>
       </c>
       <c r="E65" s="2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>10.000</t>
+          <t>3.900</t>
         </is>
       </c>
       <c r="H65" s="2" t="n">
-        <v>10</v>
+        <v>3.9</v>
       </c>
       <c r="I65" s="4" t="n"/>
     </row>
@@ -2767,12 +2767,12 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>900090</t>
+          <t>500823</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>سيفون قطعة واحدة 4" صغير ومرار</t>
+          <t>سيفون قطعة واحدة 4"×5" صغير ومرار</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -2781,7 +2781,7 @@
         </is>
       </c>
       <c r="E66" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F66" s="2" t="n">
         <v>1</v>
@@ -2802,12 +2802,12 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>500823</t>
+          <t>500462</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>سيفون قطعة واحدة 4"×5" صغير ومرار</t>
+          <t>سيفون قطعتين 4"×5" صغير ومرار</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -2816,7 +2816,7 @@
         </is>
       </c>
       <c r="E67" s="2" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F67" s="2" t="n">
         <v>1</v>
@@ -2827,7 +2827,7 @@
         </is>
       </c>
       <c r="H67" s="2" t="n">
-        <v>3.9</v>
+        <v>5.9</v>
       </c>
       <c r="I67" s="4" t="n"/>
     </row>
@@ -2837,12 +2837,12 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>500462</t>
+          <t>500810</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>سيفون قطعتين 4"×5" صغير ومرار</t>
+          <t>سيليكون شفاف اسباني</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -2851,18 +2851,18 @@
         </is>
       </c>
       <c r="E68" s="2" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="F68" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>3.900</t>
+          <t>2.500</t>
         </is>
       </c>
       <c r="H68" s="2" t="n">
-        <v>5.9</v>
+        <v>2.5</v>
       </c>
       <c r="I68" s="4" t="n"/>
     </row>
@@ -2872,12 +2872,12 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>500810</t>
+          <t>500032</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>سيليكون شفاف اسباني</t>
+          <t>شد وصل ايطالي 1/2"×16ملم</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -2886,18 +2886,18 @@
         </is>
       </c>
       <c r="E69" s="2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F69" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>2.500</t>
+          <t>1.500</t>
         </is>
       </c>
       <c r="H69" s="2" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="I69" s="4" t="n"/>
     </row>
@@ -2907,12 +2907,12 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>500032</t>
+          <t>500131</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>شد وصل ايطالي 1/2"×16ملم</t>
+          <t>شد وصل ايطالي 1/2"×20ملم</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -2921,18 +2921,18 @@
         </is>
       </c>
       <c r="E70" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F70" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="G70" s="2" t="inlineStr">
-        <is>
-          <t>1.500</t>
+      <c r="G70" s="5" t="inlineStr">
+        <is>
+          <t>0.000</t>
         </is>
       </c>
       <c r="H70" s="2" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I70" s="4" t="n"/>
     </row>
@@ -2942,12 +2942,12 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>500131</t>
+          <t>500130</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>شد وصل ايطالي 1/2"×20ملم</t>
+          <t>شد وصل ايطالي فورنارة 1/2"×16ملم</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -2956,18 +2956,18 @@
         </is>
       </c>
       <c r="E71" s="2" t="n">
-        <v>8</v>
+        <v>94</v>
       </c>
       <c r="F71" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="G71" s="5" t="inlineStr">
-        <is>
-          <t>0.000</t>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>1.500</t>
         </is>
       </c>
       <c r="H71" s="2" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="I71" s="4" t="n"/>
     </row>
@@ -2977,12 +2977,12 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>500130</t>
+          <t>500507</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>شد وصل ايطالي فورنارة 1/2"×16ملم</t>
+          <t>شد وصل سعودي 3/4"</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -2991,10 +2991,10 @@
         </is>
       </c>
       <c r="E72" s="2" t="n">
-        <v>94</v>
+        <v>8</v>
       </c>
       <c r="F72" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
@@ -3012,12 +3012,12 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>500507</t>
+          <t>500831</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>شد وصل سعودي 3/4"</t>
+          <t>صندوق نيجارا عربي ايطالي</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -3026,18 +3026,18 @@
         </is>
       </c>
       <c r="E73" s="2" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F73" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>1.500</t>
+          <t>19.000</t>
         </is>
       </c>
       <c r="H73" s="2" t="n">
-        <v>1.5</v>
+        <v>19</v>
       </c>
       <c r="I73" s="4" t="n"/>
     </row>
@@ -3047,12 +3047,12 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>500831</t>
+          <t>230074</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>صندوق نيجارا عربي ايطالي</t>
+          <t>غطاء منهل 60*60 بيج ثقيل</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -3061,18 +3061,18 @@
         </is>
       </c>
       <c r="E74" s="2" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="F74" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>19.000</t>
+          <t>12.000</t>
         </is>
       </c>
       <c r="H74" s="2" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="I74" s="4" t="n"/>
     </row>
@@ -3082,12 +3082,12 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>230074</t>
+          <t>500145</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>غطاء منهل 60*60 بيج ثقيل</t>
+          <t>غلاف انجاصة سكني</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -3096,18 +3096,18 @@
         </is>
       </c>
       <c r="E75" s="2" t="n">
+        <v>204</v>
+      </c>
+      <c r="F75" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F75" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>12.000</t>
+          <t>0.250</t>
         </is>
       </c>
       <c r="H75" s="2" t="n">
-        <v>12</v>
+        <v>0.25</v>
       </c>
       <c r="I75" s="4" t="n"/>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>500145</t>
+          <t>500447</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>غلاف انجاصة سكني</t>
+          <t>فولتراب بلاستيك 2*4 ضغط صغير ومرار</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -3131,18 +3131,18 @@
         </is>
       </c>
       <c r="E76" s="2" t="n">
-        <v>204</v>
+        <v>23</v>
       </c>
       <c r="F76" s="2" t="n">
         <v>3</v>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>0.250</t>
+          <t>4.600</t>
         </is>
       </c>
       <c r="H76" s="2" t="n">
-        <v>0.25</v>
+        <v>4.6</v>
       </c>
       <c r="I76" s="4" t="n"/>
     </row>
@@ -3152,12 +3152,12 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>500447</t>
+          <t>500446</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>فولتراب بلاستيك 2*4 ضغط صغير ومرار</t>
+          <t>فولتراب بلاستيك 3*4 ضغط صغير ومرار</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -3166,10 +3166,10 @@
         </is>
       </c>
       <c r="E77" s="2" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="F77" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
@@ -3187,12 +3187,12 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>500446</t>
+          <t>500420</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>فولتراب بلاستيك 3*4 ضغط صغير ومرار</t>
+          <t>كوع زاوية بلاستيك 2" ضغط صغير ومرار</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -3208,11 +3208,11 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>4.600</t>
+          <t>0.450</t>
         </is>
       </c>
       <c r="H78" s="2" t="n">
-        <v>4.6</v>
+        <v>0.8</v>
       </c>
       <c r="I78" s="4" t="n"/>
     </row>
@@ -3222,12 +3222,12 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>500420</t>
+          <t>500418</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>كوع زاوية بلاستيك 2" ضغط صغير ومرار</t>
+          <t>كوع زاوية بلاستيك 4" ضغط صغير ومرار</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
@@ -3236,18 +3236,18 @@
         </is>
       </c>
       <c r="E79" s="2" t="n">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="F79" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>0.450</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="H79" s="2" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="I79" s="4" t="n"/>
     </row>
@@ -3257,12 +3257,12 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>500418</t>
+          <t>500477</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>كوع زاوية بلاستيك 4" ضغط صغير ومرار</t>
+          <t>كوع زاوية سعودي 11/4"</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -3271,18 +3271,18 @@
         </is>
       </c>
       <c r="E80" s="2" t="n">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="F80" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.250</t>
         </is>
       </c>
       <c r="H80" s="2" t="n">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="I80" s="4" t="n"/>
     </row>
@@ -3292,12 +3292,12 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>500477</t>
+          <t>500475</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>كوع زاوية سعودي 11/4"</t>
+          <t>كوع زاوية سعودي 3/4"</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
@@ -3306,18 +3306,18 @@
         </is>
       </c>
       <c r="E81" s="2" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="F81" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>1.250</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="H81" s="2" t="n">
-        <v>1.25</v>
+        <v>0.5</v>
       </c>
       <c r="I81" s="4" t="n"/>
     </row>
@@ -3327,12 +3327,12 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>500475</t>
+          <t>500416</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>كوع زاوية سعودي 3/4"</t>
+          <t>كوع فاتح بلاستيك 2" ضغط صغير ومرار</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
@@ -3341,18 +3341,18 @@
         </is>
       </c>
       <c r="E82" s="2" t="n">
+        <v>74</v>
+      </c>
+      <c r="F82" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="F82" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.800</t>
         </is>
       </c>
       <c r="H82" s="2" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="I82" s="4" t="n"/>
     </row>
@@ -3362,12 +3362,12 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>500416</t>
+          <t>500414</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>كوع فاتح بلاستيك 2" ضغط صغير ومرار</t>
+          <t>كوع فاتح بلاستيك 4" ضغط صغير ومرار</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
@@ -3376,18 +3376,18 @@
         </is>
       </c>
       <c r="E83" s="2" t="n">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="F83" s="2" t="n">
         <v>4</v>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>0.800</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="H83" s="2" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="I83" s="4" t="n"/>
     </row>
@@ -3397,12 +3397,12 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>500414</t>
+          <t>500413</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>كوع فاتح بلاستيك 4" ضغط صغير ومرار</t>
+          <t>كوع فاتح بلاستيك 6" ضغط صغير ومرار</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
@@ -3411,18 +3411,18 @@
         </is>
       </c>
       <c r="E84" s="2" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="F84" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>4.600</t>
         </is>
       </c>
       <c r="H84" s="2" t="n">
-        <v>2</v>
+        <v>4.6</v>
       </c>
       <c r="I84" s="4" t="n"/>
     </row>
@@ -3432,12 +3432,12 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>500413</t>
+          <t>500439</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>كوع فاتح بلاستيك 6" ضغط صغير ومرار</t>
+          <t>كوع مع باب بلاستيك 4" ضغط صغير ومرار</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
@@ -3446,18 +3446,18 @@
         </is>
       </c>
       <c r="E85" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F85" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>4.600</t>
+          <t>2.600</t>
         </is>
       </c>
       <c r="H85" s="2" t="n">
-        <v>4.6</v>
+        <v>2.6</v>
       </c>
       <c r="I85" s="4" t="n"/>
     </row>
@@ -3467,12 +3467,12 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>500439</t>
+          <t>500141</t>
         </is>
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>كوع مع باب بلاستيك 4" ضغط صغير ومرار</t>
+          <t>كوع نجاصة ايطالي 16*1/2</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
@@ -3481,18 +3481,18 @@
         </is>
       </c>
       <c r="E86" s="2" t="n">
-        <v>8</v>
+        <v>99</v>
       </c>
       <c r="F86" s="2" t="n">
         <v>2</v>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>2.600</t>
+          <t>2.650</t>
         </is>
       </c>
       <c r="H86" s="2" t="n">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="I86" s="4" t="n"/>
     </row>
@@ -3502,12 +3502,12 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>500141</t>
+          <t>500693</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>كوع نجاصة ايطالي 16*1/2</t>
+          <t>كوع نجاصة نحاس ايطالي 20ملم×1/2"</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
@@ -3516,18 +3516,18 @@
         </is>
       </c>
       <c r="E87" s="2" t="n">
-        <v>99</v>
+        <v>4</v>
       </c>
       <c r="F87" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>2.650</t>
+          <t>4.000</t>
         </is>
       </c>
       <c r="H87" s="2" t="n">
-        <v>2.65</v>
+        <v>4</v>
       </c>
       <c r="I87" s="4" t="n"/>
     </row>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>500693</t>
+          <t>500570</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>كوع نجاصة نحاس ايطالي 20ملم×1/2"</t>
+          <t>كوليكتر ايطالي 11/4" (10 فتحة) FORNARA</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
@@ -3551,18 +3551,18 @@
         </is>
       </c>
       <c r="E88" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="F88" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="F88" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>4.000</t>
+          <t>33.500</t>
         </is>
       </c>
       <c r="H88" s="2" t="n">
-        <v>4</v>
+        <v>33.5</v>
       </c>
       <c r="I88" s="4" t="n"/>
     </row>
@@ -3572,12 +3572,12 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>500570</t>
+          <t>500571</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>كوليكتر ايطالي 11/4" (10 فتحة) FORNARA</t>
+          <t>كوليكتر ايطالي 11/4" (11 فتحة) FORNARA</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
@@ -3586,18 +3586,18 @@
         </is>
       </c>
       <c r="E89" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F89" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>33.500</t>
+          <t>36.850</t>
         </is>
       </c>
       <c r="H89" s="2" t="n">
-        <v>33.5</v>
+        <v>36.85</v>
       </c>
       <c r="I89" s="4" t="n"/>
     </row>
@@ -3607,12 +3607,12 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>500571</t>
+          <t>500572</t>
         </is>
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>كوليكتر ايطالي 11/4" (11 فتحة) FORNARA</t>
+          <t>كوليكتر ايطالي 11/4" (12 فتحة) FORNARA</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
@@ -3621,18 +3621,18 @@
         </is>
       </c>
       <c r="E90" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F90" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>36.850</t>
+          <t>40.200</t>
         </is>
       </c>
       <c r="H90" s="2" t="n">
-        <v>36.85</v>
+        <v>40.2</v>
       </c>
       <c r="I90" s="4" t="n"/>
     </row>
@@ -3642,12 +3642,12 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>500572</t>
+          <t>500565</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>كوليكتر ايطالي 11/4" (12 فتحة) FORNARA</t>
+          <t>كوليكتر ايطالي 11/4" (5 فتحة) FORNARA</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
@@ -3656,18 +3656,18 @@
         </is>
       </c>
       <c r="E91" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F91" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F91" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>40.200</t>
+          <t>16.750</t>
         </is>
       </c>
       <c r="H91" s="2" t="n">
-        <v>40.2</v>
+        <v>16.75</v>
       </c>
       <c r="I91" s="4" t="n"/>
     </row>
@@ -3677,12 +3677,12 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>500565</t>
+          <t>500412</t>
         </is>
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>كوليكتر ايطالي 11/4" (5 فتحة) FORNARA</t>
+          <t>ماسورة بلاستيك 2" ضغط صغير ومرار</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
@@ -3691,18 +3691,18 @@
         </is>
       </c>
       <c r="E92" s="2" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="F92" s="2" t="n">
         <v>2</v>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>16.750</t>
+          <t>1.500</t>
         </is>
       </c>
       <c r="H92" s="2" t="n">
-        <v>16.75</v>
+        <v>1.5</v>
       </c>
       <c r="I92" s="4" t="n"/>
     </row>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>500412</t>
+          <t>500410</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>ماسورة بلاستيك 2" ضغط صغير ومرار</t>
+          <t>ماسورة بلاستيك 4" ضغط صغير ومرار</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
@@ -3726,18 +3726,18 @@
         </is>
       </c>
       <c r="E93" s="2" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F93" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G93" s="2" t="inlineStr">
-        <is>
-          <t>1.500</t>
+        <v>4</v>
+      </c>
+      <c r="G93" s="5" t="inlineStr">
+        <is>
+          <t>2.750 / 3.300</t>
         </is>
       </c>
       <c r="H93" s="2" t="n">
-        <v>1.5</v>
+        <v>3.3</v>
       </c>
       <c r="I93" s="4" t="n"/>
     </row>
@@ -3747,12 +3747,12 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>500410</t>
+          <t>500574</t>
         </is>
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>ماسورة بلاستيك 4" ضغط صغير ومرار</t>
+          <t>ماسورة بلاستيك 5" ضغط صغير ومرار</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
@@ -3761,18 +3761,18 @@
         </is>
       </c>
       <c r="E94" s="2" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="F94" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="G94" s="5" t="inlineStr">
-        <is>
-          <t>2.750 / 3.300</t>
+        <v>2</v>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>5.000</t>
         </is>
       </c>
       <c r="H94" s="2" t="n">
-        <v>3.3</v>
+        <v>5</v>
       </c>
       <c r="I94" s="4" t="n"/>
     </row>
@@ -3782,12 +3782,12 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>500574</t>
+          <t>500409</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>ماسورة بلاستيك 5" ضغط صغير ومرار</t>
+          <t>ماسورة بلاستيك 6" ضغط صغير ومرار</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
@@ -3796,18 +3796,18 @@
         </is>
       </c>
       <c r="E95" s="2" t="n">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="F95" s="2" t="n">
         <v>2</v>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>5.000</t>
+          <t>4.900</t>
         </is>
       </c>
       <c r="H95" s="2" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="I95" s="4" t="n"/>
     </row>
@@ -3817,12 +3817,12 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>500409</t>
+          <t>500106</t>
         </is>
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>ماسورة بلاستيك 6" ضغط صغير ومرار</t>
+          <t>محبس زاوية ايطالي</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
@@ -3831,18 +3831,18 @@
         </is>
       </c>
       <c r="E96" s="2" t="n">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="F96" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>4.900</t>
+          <t>2.500</t>
         </is>
       </c>
       <c r="H96" s="2" t="n">
-        <v>4.9</v>
+        <v>2.5</v>
       </c>
       <c r="I96" s="4" t="n"/>
     </row>
@@ -3852,12 +3852,12 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>500106</t>
+          <t>500190</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>محبس زاوية ايطالي</t>
+          <t>محبس ستيم ايطالي 3/4"</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
@@ -3866,18 +3866,18 @@
         </is>
       </c>
       <c r="E97" s="2" t="n">
-        <v>62</v>
+        <v>6</v>
       </c>
       <c r="F97" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>2.500</t>
+          <t>4.000</t>
         </is>
       </c>
       <c r="H97" s="2" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="I97" s="4" t="n"/>
     </row>
@@ -3887,12 +3887,12 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>500190</t>
+          <t>500179</t>
         </is>
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t>محبس ستيم ايطالي 3/4"</t>
+          <t>محبس فراشة مع شد وصل نحاس 11/4" NTM</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
@@ -3901,14 +3901,14 @@
         </is>
       </c>
       <c r="E98" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F98" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="G98" s="2" t="inlineStr">
-        <is>
-          <t>4.000</t>
+      <c r="G98" s="5" t="inlineStr">
+        <is>
+          <t>0.000</t>
         </is>
       </c>
       <c r="H98" s="2" t="n">
@@ -3922,12 +3922,12 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>500179</t>
+          <t>500594</t>
         </is>
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>محبس فراشة مع شد وصل نحاس 11/4" NTM</t>
+          <t>محبس فرعي ايطالي 1/2" احمروازرق</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
@@ -3936,18 +3936,18 @@
         </is>
       </c>
       <c r="E99" s="2" t="n">
-        <v>8</v>
+        <v>102</v>
       </c>
       <c r="F99" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="G99" s="5" t="inlineStr">
-        <is>
-          <t>0.000</t>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>2.250</t>
         </is>
       </c>
       <c r="H99" s="2" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="I99" s="4" t="n"/>
     </row>
@@ -3957,12 +3957,12 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>500594</t>
+          <t>500283</t>
         </is>
       </c>
       <c r="C100" s="3" t="inlineStr">
         <is>
-          <t>محبس فرعي ايطالي 1/2" احمروازرق</t>
+          <t>مربط او برغي كيزر ايطالي</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
@@ -3971,18 +3971,18 @@
         </is>
       </c>
       <c r="E100" s="2" t="n">
-        <v>102</v>
+        <v>8</v>
       </c>
       <c r="F100" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>2.250</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="H100" s="2" t="n">
-        <v>2.25</v>
+        <v>1</v>
       </c>
       <c r="I100" s="4" t="n"/>
     </row>
@@ -3992,12 +3992,12 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>500283</t>
+          <t>230095</t>
         </is>
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t>مربط او برغي كيزر ايطالي</t>
+          <t>مربط كوليكتر طويل . 1 جوز</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
@@ -4006,18 +4006,18 @@
         </is>
       </c>
       <c r="E101" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F101" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>4.000</t>
         </is>
       </c>
       <c r="H101" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I101" s="4" t="n"/>
     </row>
@@ -4027,12 +4027,12 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>230095</t>
+          <t>500581</t>
         </is>
       </c>
       <c r="C102" s="3" t="inlineStr">
         <is>
-          <t>مربط كوليكتر طويل . 1 جوز</t>
+          <t>مربط مواسير ايطالي فيشر 11/4"</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
@@ -4041,18 +4041,18 @@
         </is>
       </c>
       <c r="E102" s="2" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="F102" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="G102" s="2" t="inlineStr">
-        <is>
-          <t>4.000</t>
+      <c r="G102" s="5" t="inlineStr">
+        <is>
+          <t>0.000 / 0.750</t>
         </is>
       </c>
       <c r="H102" s="2" t="n">
-        <v>4</v>
+        <v>0.75</v>
       </c>
       <c r="I102" s="4" t="n"/>
     </row>
@@ -4062,12 +4062,12 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>500581</t>
+          <t>500586</t>
         </is>
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t>مربط مواسير ايطالي فيشر 11/4"</t>
+          <t>مربط مواسير ايطالي فيشر 4"</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
@@ -4076,18 +4076,18 @@
         </is>
       </c>
       <c r="E103" s="2" t="n">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="F103" s="2" t="n">
         <v>2</v>
       </c>
       <c r="G103" s="5" t="inlineStr">
         <is>
-          <t>0.000 / 0.750</t>
+          <t>0.000 / 1.000</t>
         </is>
       </c>
       <c r="H103" s="2" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="I103" s="4" t="n"/>
     </row>
@@ -4097,12 +4097,12 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>500586</t>
+          <t>500331</t>
         </is>
       </c>
       <c r="C104" s="3" t="inlineStr">
         <is>
-          <t>مربط مواسير ايطالي فيشر 4"</t>
+          <t>مصفاة ستانلس 15*15 سم (جلدة)</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
@@ -4111,18 +4111,18 @@
         </is>
       </c>
       <c r="E104" s="2" t="n">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="F104" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="G104" s="5" t="inlineStr">
-        <is>
-          <t>0.000 / 1.000</t>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>2.500</t>
         </is>
       </c>
       <c r="H104" s="2" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="I104" s="4" t="n"/>
     </row>
@@ -4132,12 +4132,12 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>500331</t>
+          <t>701959</t>
         </is>
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t>مصفاة ستانلس 15*15 سم (جلدة)</t>
+          <t>مصفاة ستانلس 15*15 سم (كلين اوت) ماركوبولو</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
@@ -4146,18 +4146,18 @@
         </is>
       </c>
       <c r="E105" s="2" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="F105" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>2.500</t>
+          <t>6.000</t>
         </is>
       </c>
       <c r="H105" s="2" t="n">
-        <v>2.5</v>
+        <v>6</v>
       </c>
       <c r="I105" s="4" t="n"/>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>701959</t>
+          <t>500425</t>
         </is>
       </c>
       <c r="C106" s="3" t="inlineStr">
         <is>
-          <t>مصفاة ستانلس 15*15 سم (كلين اوت) ماركوبولو</t>
+          <t>مفة بلاستيك 2" ضغط صغير ومرار</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
@@ -4181,18 +4181,18 @@
         </is>
       </c>
       <c r="E106" s="2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F106" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>6.000</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="H106" s="2" t="n">
-        <v>6</v>
+        <v>0.5</v>
       </c>
       <c r="I106" s="4" t="n"/>
     </row>
@@ -4202,12 +4202,12 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>500425</t>
+          <t>500422</t>
         </is>
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t>مفة بلاستيك 2" ضغط صغير ومرار</t>
+          <t>مفة بلاستيك 4" ضغط صغير ومرار</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
@@ -4216,18 +4216,18 @@
         </is>
       </c>
       <c r="E107" s="2" t="n">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="F107" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G107" s="2" t="inlineStr">
-        <is>
-          <t>0.500</t>
+        <v>2</v>
+      </c>
+      <c r="G107" s="5" t="inlineStr">
+        <is>
+          <t>0.900 / 1.000</t>
         </is>
       </c>
       <c r="H107" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="I107" s="4" t="n"/>
     </row>
@@ -4237,12 +4237,12 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>500422</t>
+          <t>500492</t>
         </is>
       </c>
       <c r="C108" s="3" t="inlineStr">
         <is>
-          <t>مفة بلاستيك 4" ضغط صغير ومرار</t>
+          <t>مفة سعودي 11/4"</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
@@ -4251,14 +4251,14 @@
         </is>
       </c>
       <c r="E108" s="2" t="n">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="F108" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G108" s="5" t="inlineStr">
-        <is>
-          <t>0.900 / 1.000</t>
+        <v>1</v>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>1.000</t>
         </is>
       </c>
       <c r="H108" s="2" t="n">
@@ -4272,12 +4272,12 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>500492</t>
+          <t>500383</t>
         </is>
       </c>
       <c r="C109" s="3" t="inlineStr">
         <is>
-          <t>مفة سعودي 11/4"</t>
+          <t>منظف مواسير 1/4 ك</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
@@ -4286,18 +4286,18 @@
         </is>
       </c>
       <c r="E109" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F109" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>2.500</t>
         </is>
       </c>
       <c r="H109" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I109" s="4" t="n"/>
     </row>
@@ -4307,12 +4307,12 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>500383</t>
+          <t>500371</t>
         </is>
       </c>
       <c r="C110" s="3" t="inlineStr">
         <is>
-          <t>منظف مواسير 1/4 ك</t>
+          <t>منهل قاعدة صغير ومرار (فيرجن)</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
@@ -4321,14 +4321,14 @@
         </is>
       </c>
       <c r="E110" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F110" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="G110" s="2" t="inlineStr">
-        <is>
-          <t>2.500</t>
+      <c r="G110" s="5" t="inlineStr">
+        <is>
+          <t>0.000</t>
         </is>
       </c>
       <c r="H110" s="2" t="n">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>500371</t>
+          <t>500221</t>
         </is>
       </c>
       <c r="C111" s="3" t="inlineStr">
         <is>
-          <t>منهل قاعدة صغير ومرار (فيرجن)</t>
+          <t>نبل كروم مشكل ايطالي 2.5سم</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
@@ -4356,18 +4356,18 @@
         </is>
       </c>
       <c r="E111" s="2" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="F111" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="G111" s="5" t="inlineStr">
-        <is>
-          <t>0.000</t>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>1.250</t>
         </is>
       </c>
       <c r="H111" s="2" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="I111" s="4" t="n"/>
     </row>
@@ -4377,12 +4377,12 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>500221</t>
+          <t>500153</t>
         </is>
       </c>
       <c r="C112" s="3" t="inlineStr">
         <is>
-          <t>نبل كروم مشكل ايطالي 2.5سم</t>
+          <t>نبل مجوز نحاس ايطالي 11/4" وصلة كوليكتر (ذكر ذكر)</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
@@ -4391,18 +4391,18 @@
         </is>
       </c>
       <c r="E112" s="2" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="F112" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>1.250</t>
+          <t>4.000</t>
         </is>
       </c>
       <c r="H112" s="2" t="n">
-        <v>1.25</v>
+        <v>4</v>
       </c>
       <c r="I112" s="4" t="n"/>
     </row>
@@ -4412,12 +4412,12 @@
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>500153</t>
+          <t>500452</t>
         </is>
       </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t>نبل مجوز نحاس ايطالي 11/4" وصلة كوليكتر (ذكر ذكر)</t>
+          <t>نقاصة بلاستيك 2*3 صغير ومرار</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
@@ -4426,18 +4426,18 @@
         </is>
       </c>
       <c r="E113" s="2" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F113" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>4.000</t>
+          <t>0.800</t>
         </is>
       </c>
       <c r="H113" s="2" t="n">
-        <v>4</v>
+        <v>0.8</v>
       </c>
       <c r="I113" s="4" t="n"/>
     </row>
@@ -4447,12 +4447,12 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>500452</t>
+          <t>500769</t>
         </is>
       </c>
       <c r="C114" s="3" t="inlineStr">
         <is>
-          <t>نقاصة بلاستيك 2*3 صغير ومرار</t>
+          <t>نقاصة حديد 3/4"×1" صيني</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
@@ -4461,18 +4461,18 @@
         </is>
       </c>
       <c r="E114" s="2" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F114" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>0.800</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="H114" s="2" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="I114" s="4" t="n"/>
     </row>
@@ -4482,12 +4482,12 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>500769</t>
+          <t>500467</t>
         </is>
       </c>
       <c r="C115" s="3" t="inlineStr">
         <is>
-          <t>نقاصة حديد 3/4"×1" صيني</t>
+          <t>نقاصة طويلة بلاستيك 2"*3" ضغط صغير ومرار</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
@@ -4496,18 +4496,18 @@
         </is>
       </c>
       <c r="E115" s="2" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F115" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.800</t>
         </is>
       </c>
       <c r="H115" s="2" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="I115" s="4" t="n"/>
     </row>
@@ -4517,12 +4517,12 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>500467</t>
+          <t>500389</t>
         </is>
       </c>
       <c r="C116" s="3" t="inlineStr">
         <is>
-          <t>نقاصة طويلة بلاستيك 2"*3" ضغط صغير ومرار</t>
+          <t>نهاية كوليكتر 11/4" اندبيس</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
@@ -4531,18 +4531,18 @@
         </is>
       </c>
       <c r="E116" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F116" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="G116" s="2" t="inlineStr">
-        <is>
-          <t>0.800</t>
+      <c r="G116" s="5" t="inlineStr">
+        <is>
+          <t>0.000</t>
         </is>
       </c>
       <c r="H116" s="2" t="n">
-        <v>0.8</v>
+        <v>4.5</v>
       </c>
       <c r="I116" s="4" t="n"/>
     </row>
@@ -4552,12 +4552,12 @@
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>500389</t>
+          <t>500578</t>
         </is>
       </c>
       <c r="C117" s="3" t="inlineStr">
         <is>
-          <t>نهاية كوليكتر 11/4" اندبيس</t>
+          <t>هواية 1/2" (جاكوميني) ايطالي</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
@@ -4577,7 +4577,7 @@
         </is>
       </c>
       <c r="H117" s="2" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="I117" s="4" t="n"/>
     </row>
@@ -4587,12 +4587,12 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>500578</t>
+          <t>500431</t>
         </is>
       </c>
       <c r="C118" s="3" t="inlineStr">
         <is>
-          <t>هواية 1/2" (جاكوميني) ايطالي</t>
+          <t>واي بلاستيك 4" ضغط صغير ومرار</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
@@ -4601,18 +4601,18 @@
         </is>
       </c>
       <c r="E118" s="2" t="n">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="F118" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G118" s="5" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>2.750 / 3.900</t>
         </is>
       </c>
       <c r="H118" s="2" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="I118" s="4" t="n"/>
     </row>
@@ -4622,12 +4622,12 @@
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>500431</t>
+          <t>500449</t>
         </is>
       </c>
       <c r="C119" s="3" t="inlineStr">
         <is>
-          <t>واي بلاستيك 4" ضغط صغير ومرار</t>
+          <t>وصلة فلتراب 5" صغير ومرار</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
@@ -4636,18 +4636,18 @@
         </is>
       </c>
       <c r="E119" s="2" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F119" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="G119" s="5" t="inlineStr">
-        <is>
-          <t>2.750 / 3.900</t>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>1.300</t>
         </is>
       </c>
       <c r="H119" s="2" t="n">
-        <v>3.9</v>
+        <v>1.3</v>
       </c>
       <c r="I119" s="4" t="n"/>
     </row>
@@ -4657,12 +4657,12 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>500449</t>
+          <t>500368</t>
         </is>
       </c>
       <c r="C120" s="3" t="inlineStr">
         <is>
-          <t>وصلة فلتراب 5" صغير ومرار</t>
+          <t>وصلة منهل صغير ومرار (عادي)</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
@@ -4671,18 +4671,18 @@
         </is>
       </c>
       <c r="E120" s="2" t="n">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="F120" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="G120" s="2" t="inlineStr">
-        <is>
-          <t>1.300</t>
+        <v>1</v>
+      </c>
+      <c r="G120" s="5" t="inlineStr">
+        <is>
+          <t>0.000</t>
         </is>
       </c>
       <c r="H120" s="2" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="I120" s="4" t="n"/>
     </row>
@@ -4692,12 +4692,12 @@
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>500368</t>
+          <t>500369</t>
         </is>
       </c>
       <c r="C121" s="3" t="inlineStr">
         <is>
-          <t>وصلة منهل صغير ومرار (عادي)</t>
+          <t>وصلة منهل صغير ومرار (فيرجن)</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
@@ -4706,7 +4706,7 @@
         </is>
       </c>
       <c r="E121" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F121" s="2" t="n">
         <v>1</v>
@@ -4727,32 +4727,32 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>500369</t>
+          <t>900091</t>
         </is>
       </c>
       <c r="C122" s="3" t="inlineStr">
         <is>
-          <t>وصلة منهل صغير ومرار (فيرجن)</t>
+          <t>بربيش كهرباء 16 ملم اسود</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>صحي</t>
+          <t>كهرباء</t>
         </is>
       </c>
       <c r="E122" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="F122" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>2.000</t>
+        </is>
+      </c>
+      <c r="H122" s="2" t="n">
         <v>2</v>
-      </c>
-      <c r="F122" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G122" s="5" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-      <c r="H122" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="I122" s="4" t="n"/>
     </row>
@@ -4762,12 +4762,12 @@
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>900091</t>
+          <t>900088</t>
         </is>
       </c>
       <c r="C123" s="3" t="inlineStr">
         <is>
-          <t>بربيش كهرباء 16 ملم اسود</t>
+          <t>بربيش كهرباء 19 ملم ابيض</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
@@ -4776,14 +4776,14 @@
         </is>
       </c>
       <c r="E123" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="F123" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="G123" s="2" t="inlineStr">
-        <is>
-          <t>2.000</t>
+      <c r="G123" s="5" t="inlineStr">
+        <is>
+          <t>1.900 / 2.000</t>
         </is>
       </c>
       <c r="H123" s="2" t="n">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>900088</t>
+          <t>900902</t>
         </is>
       </c>
       <c r="C124" s="3" t="inlineStr">
         <is>
-          <t>بربيش كهرباء 19 ملم ابيض</t>
+          <t>بربيش كهرباء 19 ملم اسود</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
@@ -4811,14 +4811,14 @@
         </is>
       </c>
       <c r="E124" s="2" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="F124" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="G124" s="5" t="inlineStr">
-        <is>
-          <t>1.900 / 2.000</t>
+        <v>1</v>
+      </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>2.000</t>
         </is>
       </c>
       <c r="H124" s="2" t="n">
@@ -4832,12 +4832,12 @@
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>900902</t>
+          <t>900907</t>
         </is>
       </c>
       <c r="C125" s="3" t="inlineStr">
         <is>
-          <t>بربيش كهرباء 19 ملم اسود</t>
+          <t>ماسورة كهرباء 25ملم اسود - ربطة (30 ماسورة)</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
@@ -4846,18 +4846,18 @@
         </is>
       </c>
       <c r="E125" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F125" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G125" s="2" t="inlineStr">
-        <is>
-          <t>2.000</t>
+        <v>3</v>
+      </c>
+      <c r="G125" s="5" t="inlineStr">
+        <is>
+          <t>0.000</t>
         </is>
       </c>
       <c r="H125" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I125" s="4" t="n"/>
     </row>
@@ -4867,12 +4867,12 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>900907</t>
+          <t>900908</t>
         </is>
       </c>
       <c r="C126" s="3" t="inlineStr">
         <is>
-          <t>ماسورة كهرباء 25ملم اسود - ربطة (30 ماسورة)</t>
+          <t>مفة كهرباء 25ملم اسود</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
@@ -4881,10 +4881,10 @@
         </is>
       </c>
       <c r="E126" s="2" t="n">
-        <v>8</v>
+        <v>200</v>
       </c>
       <c r="F126" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G126" s="5" t="inlineStr">
         <is>
@@ -4895,41 +4895,6 @@
         <v>0</v>
       </c>
       <c r="I126" s="4" t="n"/>
-    </row>
-    <row r="127" ht="19" customHeight="1">
-      <c r="A127" s="2" t="n">
-        <v>126</v>
-      </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>900908</t>
-        </is>
-      </c>
-      <c r="C127" s="3" t="inlineStr">
-        <is>
-          <t>مفة كهرباء 25ملم اسود</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="inlineStr">
-        <is>
-          <t>كهرباء</t>
-        </is>
-      </c>
-      <c r="E127" s="2" t="n">
-        <v>200</v>
-      </c>
-      <c r="F127" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G127" s="5" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-      <c r="H127" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I127" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
